--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513598_ELIMINATORIAS12FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513598_ELIMINATORIAS12FINAL_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. FABREGA URPINA</t>
+          <t>F. STUTZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1043</v>
+        <v>3.2644</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6329</v>
+        <v>-0.5674</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4714</v>
+        <v>3.8317</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3527</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6093</v>
+        <v>0.6322</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.0781</v>
       </c>
       <c r="J2" t="n">
-        <v>2.528</v>
+        <v>-0.1535</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8243</v>
+        <v>0.5314</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.2963</v>
+        <v>-0.6848</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8247</v>
+        <v>0.8637</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.215</v>
+        <v>0.1008</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0397</v>
+        <v>0.7629</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4049</v>
+        <v>1.0123</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.227</v>
+        <v>-1.2147</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8221</v>
+        <v>2.227</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6221</v>
+        <v>0.3517</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4858</v>
+        <v>-0.2962</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1362</v>
+        <v>0.6479</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.4655</v>
+        <v>1.1902</v>
       </c>
       <c r="W2" t="n">
-        <v>0.846</v>
+        <v>1.097</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.3116</v>
+        <v>0.09320000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. STUTZ</t>
+          <t>M. ANDREATTA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9319</v>
+        <v>2.7311</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.1592</v>
+        <v>0.1667</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0911</v>
+        <v>2.5643</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7102000000000001</v>
+        <v>2.0214</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6322</v>
+        <v>0.8302</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0781</v>
+        <v>1.1912</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1535</v>
+        <v>1.2915</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5314</v>
+        <v>0.6717</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6848</v>
+        <v>0.6198</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8637</v>
+        <v>0.73</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1008</v>
+        <v>0.1586</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7629</v>
+        <v>0.5714</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0123</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.2147</v>
+        <v>-1.0123</v>
       </c>
       <c r="R3" t="n">
-        <v>2.227</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0192</v>
+        <v>0.3574</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.888</v>
+        <v>-0.1125</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9072</v>
+        <v>0.4699</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1902</v>
+        <v>0.7572</v>
       </c>
       <c r="W3" t="n">
-        <v>1.097</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.7572</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ANDREATTA</t>
+          <t>O. RUSSELL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2225</v>
+        <v>2.6264</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.169</v>
+        <v>1.1683</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3915</v>
+        <v>1.4581</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0214</v>
+        <v>3.8756</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8302</v>
+        <v>-0.0012</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1912</v>
+        <v>3.8768</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2915</v>
+        <v>4.2779</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6717</v>
+        <v>0.0566</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6198</v>
+        <v>4.2213</v>
       </c>
       <c r="M4" t="n">
-        <v>0.73</v>
+        <v>-0.4022</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1586</v>
+        <v>-0.0578</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5714</v>
+        <v>-0.3444</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4049</v>
+        <v>-1.4172</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0123</v>
+        <v>-3.0368</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6074000000000001</v>
+        <v>1.6196</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1512</v>
+        <v>-0.1518</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4482</v>
+        <v>-0.5747</v>
       </c>
       <c r="U4" t="n">
-        <v>0.297</v>
+        <v>0.4228</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7572</v>
+        <v>0.3198</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5019</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7572</v>
+        <v>-0.1821</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. RUSSELL</t>
+          <t>R. FABREGA URPINA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8571</v>
+        <v>2.3008</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6008</v>
+        <v>1.2904</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2564</v>
+        <v>1.0104</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8756</v>
+        <v>3.3527</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0012</v>
+        <v>2.6093</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8768</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2779</v>
+        <v>2.528</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0566</v>
+        <v>2.8243</v>
       </c>
       <c r="L5" t="n">
-        <v>4.2213</v>
+        <v>-0.2963</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4022</v>
+        <v>0.8247</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0578</v>
+        <v>-0.215</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3444</v>
+        <v>1.0397</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.4172</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.0368</v>
+        <v>-2.227</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6196</v>
+        <v>1.8221</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9211</v>
+        <v>0.8185</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1422</v>
+        <v>0.1433</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2211</v>
+        <v>0.6752</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3198</v>
+        <v>-1.4655</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5019</v>
+        <v>0.846</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1821</v>
+        <v>-2.3116</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5191</v>
+        <v>0.2927</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.9452</v>
+        <v>-2.9123</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4643</v>
+        <v>3.205</v>
       </c>
       <c r="G6" t="n">
         <v>0.1656</v>
@@ -922,13 +922,13 @@
         <v>2.4294</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8394</v>
+        <v>0.613</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0678</v>
+        <v>-0.0349</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9072</v>
+        <v>0.6479</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6883</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5194</v>
+        <v>-0.9006</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3562</v>
+        <v>0.1473</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1631</v>
+        <v>-1.0479</v>
       </c>
       <c r="G7" t="n">
         <v>0.7257</v>
@@ -1000,13 +1000,13 @@
         <v>0.6074000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3384</v>
+        <v>0.2804</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7044</v>
+        <v>-0.2008</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3659</v>
+        <v>0.4812</v>
       </c>
       <c r="V7" t="n">
         <v>-2.3116</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9756</v>
+        <v>-1.9495</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2007</v>
+        <v>-1.0882</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7749</v>
+        <v>-0.8613</v>
       </c>
       <c r="G8" t="n">
         <v>0.2529</v>
@@ -1078,13 +1078,13 @@
         <v>1.2147</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2936</v>
+        <v>0.3197</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1196</v>
+        <v>-0.0071</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4132</v>
+        <v>0.3268</v>
       </c>
       <c r="V8" t="n">
         <v>-2.7246</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MUKENDI MUKENDI</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7343</v>
+        <v>-2.3998</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7731</v>
+        <v>-3.1178</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9612000000000001</v>
+        <v>0.7181</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.8309</v>
+        <v>-1.7784</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.4511</v>
+        <v>0.08</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3798</v>
+        <v>-1.8583</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.017</v>
+        <v>-1.5914</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.017</v>
+        <v>-0.1982</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.3932</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8139</v>
+        <v>-0.187</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4341</v>
+        <v>0.2782</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3798</v>
+        <v>-0.4651</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.4049</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.2147</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6074000000000001</v>
+        <v>1.6196</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0089</v>
+        <v>0.0951</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2439</v>
+        <v>-0.3117</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2527</v>
+        <v>0.4068</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5019</v>
+        <v>-1.1214</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5019</v>
+        <v>-1.1214</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>M. MUKENDI MUKENDI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1297</v>
+        <v>-2.9707</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.502</v>
+        <v>-1.9808</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3723</v>
+        <v>-0.99</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7784</v>
+        <v>-2.8309</v>
       </c>
       <c r="H10" t="n">
-        <v>0.08</v>
+        <v>-2.4511</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8583</v>
+        <v>-0.3798</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5914</v>
+        <v>-2.017</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1982</v>
+        <v>-2.017</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3932</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.187</v>
+        <v>-0.8139</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2782</v>
+        <v>-0.4341</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4651</v>
+        <v>-0.3798</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4049</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.2147</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6196</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6349</v>
+        <v>-0.2453</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6959</v>
+        <v>0.0362</v>
       </c>
       <c r="U10" t="n">
-        <v>0.061</v>
+        <v>-0.2815</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1214</v>
+        <v>-0.5019</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1214</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.726</v>
+        <v>-3.8836</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2381</v>
+        <v>-3.655</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4879</v>
+        <v>-0.2286</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3123</v>
@@ -1312,13 +1312,13 @@
         <v>0.4049</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6162</v>
+        <v>0.2262</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5763</v>
+        <v>0.0068</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0399</v>
+        <v>0.2194</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1902</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4501</v>
+        <v>-0.8888000000000003</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.1098</v>
+        <v>-10.5488</v>
       </c>
       <c r="F12" t="n">
-        <v>9.6599</v>
+        <v>9.659799999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>4.182500000000001</v>
+        <v>4.182499999999999</v>
       </c>
       <c r="H12" t="n">
         <v>3.756200000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4266000000000001</v>
+        <v>0.4266000000000005</v>
       </c>
       <c r="J12" t="n">
         <v>2.549699999999999</v>
@@ -1369,19 +1369,19 @@
         <v>4.7306</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.180800000000001</v>
+        <v>-2.1808</v>
       </c>
       <c r="M12" t="n">
         <v>1.6331</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9742999999999999</v>
+        <v>-0.9743000000000002</v>
       </c>
       <c r="O12" t="n">
-        <v>2.6075</v>
+        <v>2.607500000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>9.999999999987796e-05</v>
+        <v>9.999999999976694e-05</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.1596</v>
@@ -1390,22 +1390,22 @@
         <v>13.1595</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1036000000000002</v>
+        <v>2.6649</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.9127</v>
+        <v>-1.3516</v>
       </c>
       <c r="U12" t="n">
-        <v>4.0162</v>
+        <v>4.0164</v>
       </c>
       <c r="V12" t="n">
-        <v>-7.736299999999999</v>
+        <v>-7.7363</v>
       </c>
       <c r="W12" t="n">
         <v>1.4124</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.148799999999998</v>
+        <v>-9.1488</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4869</v>
+        <v>4.7348</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1959</v>
+        <v>1.2997</v>
       </c>
       <c r="F13" t="n">
-        <v>3.291</v>
+        <v>3.4351</v>
       </c>
       <c r="G13" t="n">
         <v>2.3909</v>
@@ -1468,13 +1468,13 @@
         <v>2.227</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3089</v>
+        <v>-0.061</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5885</v>
+        <v>-0.4847</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2797</v>
+        <v>0.4238</v>
       </c>
       <c r="V13" t="n">
         <v>1.1902</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3174</v>
+        <v>3.6288</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4431</v>
+        <v>2.7545</v>
       </c>
       <c r="F14" t="n">
         <v>0.8743</v>
@@ -1546,10 +1546,10 @@
         <v>1.2147</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1488</v>
+        <v>0.1627</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6403</v>
+        <v>-0.3289</v>
       </c>
       <c r="U14" t="n">
         <v>0.4915</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2805</v>
+        <v>2.8427</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7859</v>
+        <v>-0.4744</v>
       </c>
       <c r="F15" t="n">
-        <v>4.0663</v>
+        <v>3.3172</v>
       </c>
       <c r="G15" t="n">
         <v>0.9503</v>
@@ -1624,13 +1624,13 @@
         <v>2.4294</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0063</v>
+        <v>0.5685</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9727</v>
+        <v>-0.6613</v>
       </c>
       <c r="U15" t="n">
-        <v>1.979</v>
+        <v>1.2298</v>
       </c>
       <c r="V15" t="n">
         <v>-0.09320000000000001</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6102</v>
+        <v>1.9468</v>
       </c>
       <c r="E16" t="n">
-        <v>1.584</v>
+        <v>0.4421</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0262</v>
+        <v>1.5048</v>
       </c>
       <c r="G16" t="n">
         <v>2.6627</v>
@@ -1702,13 +1702,13 @@
         <v>1.0123</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9113</v>
+        <v>0.2479</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3079</v>
+        <v>0.1659</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3966</v>
+        <v>0.0819</v>
       </c>
       <c r="V16" t="n">
         <v>0.2509</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3558</v>
+        <v>0.7076</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7511</v>
+        <v>-0.6473</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1069</v>
+        <v>1.3549</v>
       </c>
       <c r="G17" t="n">
         <v>1.0845</v>
@@ -1780,13 +1780,13 @@
         <v>0.6074000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4655</v>
+        <v>-0.1137</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4482</v>
+        <v>-0.3444</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0173</v>
+        <v>0.2307</v>
       </c>
       <c r="V17" t="n">
         <v>0.3442</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0949</v>
       </c>
       <c r="E18" t="n">
         <v>-0.2718</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2802</v>
+        <v>0.3667</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0595</v>
@@ -1858,13 +1858,13 @@
         <v>0.2025</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1345</v>
+        <v>-0.048</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1921</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0576</v>
+        <v>0.1441</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7436</v>
+        <v>0.0925</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9535</v>
+        <v>-2.5382</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2098</v>
+        <v>2.6307</v>
       </c>
       <c r="G19" t="n">
         <v>-4.3378</v>
@@ -1936,13 +1936,13 @@
         <v>2.227</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3936</v>
+        <v>0.4426</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0368</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6432</v>
+        <v>1.0641</v>
       </c>
       <c r="V19" t="n">
         <v>2.9755</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. HIERREZUELO SERER</t>
+          <t>V. AGUILAR HERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.995</v>
+        <v>-2.6427</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.4065</v>
+        <v>-1.9502</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4116</v>
+        <v>-0.6925</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5854</v>
+        <v>-1.1877</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9095</v>
+        <v>-1.1465</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6758</v>
+        <v>-0.0412</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.0374</v>
+        <v>0.6249</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0804</v>
+        <v>-0.4557</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.957</v>
+        <v>1.0806</v>
       </c>
       <c r="M20" t="n">
-        <v>0.452</v>
+        <v>-1.8126</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8292</v>
+        <v>-0.6908</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2812</v>
+        <v>-1.1218</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8221</v>
+        <v>-2.6319</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.0368</v>
+        <v>-3.2392</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2147</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3192</v>
+        <v>-0.0134</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3324</v>
+        <v>-0.7771</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6516</v>
+        <v>0.7637</v>
       </c>
       <c r="V20" t="n">
-        <v>0.09320000000000001</v>
+        <v>1.1902</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.4411</v>
       </c>
       <c r="X20" t="n">
-        <v>0.09320000000000001</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. AGUILAR HERNANDEZ</t>
+          <t>J. HIERREZUELO SERER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0869</v>
+        <v>-2.9547</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2617</v>
+        <v>-5.5103</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8253</v>
+        <v>2.5556</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1877</v>
+        <v>-1.5854</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1465</v>
+        <v>-0.9095</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0412</v>
+        <v>-0.6758</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6249</v>
+        <v>-2.0374</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4557</v>
+        <v>-0.0804</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0806</v>
+        <v>-1.957</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8126</v>
+        <v>0.452</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6908</v>
+        <v>-0.8292</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1218</v>
+        <v>1.2812</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.6319</v>
+        <v>-1.8221</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.2392</v>
+        <v>-3.0368</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6074000000000001</v>
+        <v>1.2147</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4576</v>
+        <v>0.3595</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0885</v>
+        <v>-0.4362</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6309</v>
+        <v>0.7957</v>
       </c>
       <c r="V21" t="n">
-        <v>1.1902</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4411</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2509</v>
+        <v>0.09320000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7836</v>
+        <v>-3.6165</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4523</v>
+        <v>-2.7638</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3313</v>
+        <v>-0.8527</v>
       </c>
       <c r="G22" t="n">
         <v>-3.6276</v>
@@ -2170,13 +2170,13 @@
         <v>1.4172</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4315</v>
+        <v>-0.2644</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0245</v>
+        <v>-0.336</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4069</v>
+        <v>0.0716</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9393</v>
@@ -2203,25 +2203,25 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.450200000000001</v>
+        <v>4.834200000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.659800000000001</v>
+        <v>-9.659700000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>13.1097</v>
+        <v>14.4941</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.182700000000001</v>
+        <v>-4.1827</v>
       </c>
       <c r="H23" t="n">
         <v>-3.7563</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4264999999999998</v>
+        <v>-0.4264999999999995</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.632999999999999</v>
+        <v>-1.633</v>
       </c>
       <c r="K23" t="n">
         <v>0.9743999999999997</v>
@@ -2233,13 +2233,13 @@
         <v>-2.5496</v>
       </c>
       <c r="N23" t="n">
-        <v>-4.7306</v>
+        <v>-4.730600000000001</v>
       </c>
       <c r="O23" t="n">
         <v>2.181</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>-13.1595</v>
@@ -2248,13 +2248,13 @@
         <v>13.1596</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1036000000000001</v>
+        <v>1.2807</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.0161</v>
+        <v>-4.0163</v>
       </c>
       <c r="U23" t="n">
-        <v>3.9127</v>
+        <v>5.296900000000001</v>
       </c>
       <c r="V23" t="n">
         <v>7.736299999999999</v>
